--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EXL PYTHON\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DCC20CC-E487-4F87-AF5C-72056307AC85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2582C3-9FEA-48B1-A75C-27B4E4DCD41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1139,20 +1139,22 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
+      <c r="B9" s="14">
+        <v>420</v>
+      </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="14"/>
       <c r="G9" s="14"/>
       <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>420</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1020</v>
       </c>
       <c r="K9" s="16"/>
       <c r="L9" s="16"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2582C3-9FEA-48B1-A75C-27B4E4DCD41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{302087B4-5809-49CF-B8DC-2B3AEA0F7115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>no classes</t>
   </si>
 </sst>
 </file>
@@ -1138,94 +1141,188 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
+      <c r="A9" s="13">
+        <v>46254</v>
+      </c>
       <c r="B9" s="14">
-        <v>420</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
+        <v>360</v>
+      </c>
+      <c r="C9" s="14">
+        <v>50</v>
+      </c>
+      <c r="D9" s="14">
+        <v>240</v>
+      </c>
+      <c r="E9" s="14">
+        <v>60</v>
+      </c>
+      <c r="F9" s="14">
+        <v>150</v>
+      </c>
+      <c r="G9" s="14">
+        <v>3</v>
+      </c>
+      <c r="H9" s="14">
+        <v>60</v>
+      </c>
       <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>420</v>
+        <v>920</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>1020</v>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>520</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B10" s="14">
+        <v>300</v>
+      </c>
+      <c r="C10" s="14">
+        <v>60</v>
+      </c>
+      <c r="D10" s="14">
+        <v>180</v>
+      </c>
+      <c r="E10" s="14">
+        <v>80</v>
+      </c>
+      <c r="F10" s="14">
+        <v>200</v>
+      </c>
+      <c r="G10" s="14">
+        <v>4</v>
+      </c>
+      <c r="H10" s="14">
+        <v>60</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B11" s="14">
+        <v>300</v>
+      </c>
+      <c r="C11" s="14">
+        <v>20</v>
+      </c>
+      <c r="D11" s="14">
+        <v>240</v>
+      </c>
+      <c r="E11" s="14">
+        <v>60</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>80</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>700</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>740</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B12" s="14">
+        <v>240</v>
+      </c>
+      <c r="C12" s="14">
+        <v>50</v>
+      </c>
+      <c r="D12" s="14">
+        <v>240</v>
+      </c>
+      <c r="E12" s="14">
+        <v>50</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>50</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>810</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{302087B4-5809-49CF-B8DC-2B3AEA0F7115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951022DC-24CC-4B37-9E72-08E9C2E1FB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1325,26 +1325,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B13" s="14">
+        <v>300</v>
+      </c>
+      <c r="C13" s="14">
+        <v>40</v>
+      </c>
+      <c r="D13" s="14">
+        <v>360</v>
+      </c>
+      <c r="E13" s="14">
+        <v>90</v>
+      </c>
+      <c r="F13" s="14">
+        <v>250</v>
+      </c>
+      <c r="G13" s="14">
+        <v>5</v>
+      </c>
+      <c r="H13" s="14">
+        <v>50</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951022DC-24CC-4B37-9E72-08E9C2E1FB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7B4E07-5ADB-45E4-93DB-BF0CA5E7ED5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>no classes</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -1371,26 +1374,50 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B14" s="14">
+        <v>240</v>
+      </c>
+      <c r="C14" s="14">
+        <v>20</v>
+      </c>
+      <c r="D14" s="14">
+        <v>300</v>
+      </c>
+      <c r="E14" s="14">
+        <v>120</v>
+      </c>
+      <c r="F14" s="14">
+        <v>400</v>
+      </c>
+      <c r="G14" s="14">
+        <v>8</v>
+      </c>
+      <c r="H14" s="14">
+        <v>40</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7B4E07-5ADB-45E4-93DB-BF0CA5E7ED5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C879B6B0-5CF9-4D02-BA2F-A96FF77BC3E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>tired</t>
   </si>
 </sst>
 </file>
@@ -1420,26 +1423,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B15" s="14">
+        <v>300</v>
+      </c>
+      <c r="C15" s="14">
+        <v>80</v>
+      </c>
+      <c r="D15" s="14">
+        <v>240</v>
+      </c>
+      <c r="E15" s="14">
+        <v>70</v>
+      </c>
+      <c r="F15" s="14">
+        <v>350</v>
+      </c>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="14">
+        <v>50</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C879B6B0-5CF9-4D02-BA2F-A96FF77BC3E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B62376-FC06-49C1-A8E7-63EB3F883980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>tired</t>
+  </si>
+  <si>
+    <t>booring day</t>
   </si>
 </sst>
 </file>
@@ -1469,26 +1472,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B16" s="14">
+        <v>420</v>
+      </c>
+      <c r="C16" s="14">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>300</v>
+      </c>
+      <c r="E16" s="14">
+        <v>40</v>
+      </c>
+      <c r="F16" s="14">
+        <v>200</v>
+      </c>
+      <c r="G16" s="14">
+        <v>4</v>
+      </c>
+      <c r="H16" s="14">
+        <v>60</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B62376-FC06-49C1-A8E7-63EB3F883980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6FCA3A-0905-47D6-A28B-38038D22B6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,15 @@
   </si>
   <si>
     <t>booring day</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>good day</t>
   </si>
 </sst>
 </file>
@@ -1491,7 +1500,7 @@
         <v>200</v>
       </c>
       <c r="G16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16" s="14">
         <v>60</v>
@@ -1518,26 +1527,50 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B17" s="14">
+        <v>240</v>
+      </c>
+      <c r="C17" s="14">
+        <v>20</v>
+      </c>
+      <c r="D17" s="14">
+        <v>360</v>
+      </c>
+      <c r="E17" s="14">
+        <v>180</v>
+      </c>
+      <c r="F17" s="14">
+        <v>200</v>
+      </c>
+      <c r="G17" s="14">
+        <v>4</v>
+      </c>
+      <c r="H17" s="14">
+        <v>50</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6FCA3A-0905-47D6-A28B-38038D22B6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0A940A-D7F7-48FF-808A-97AC4F667EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1573,92 +1573,188 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B18" s="14">
+        <v>300</v>
+      </c>
+      <c r="C18" s="14">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
+        <v>360</v>
+      </c>
+      <c r="E18" s="14">
+        <v>50</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>70</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B19" s="14">
+        <v>320</v>
+      </c>
+      <c r="C19" s="14">
+        <v>50</v>
+      </c>
+      <c r="D19" s="14">
+        <v>350</v>
+      </c>
+      <c r="E19" s="14">
+        <v>60</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>50</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>610</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46173</v>
+      </c>
+      <c r="B20" s="14">
+        <v>400</v>
+      </c>
+      <c r="C20" s="14">
+        <v>50</v>
+      </c>
+      <c r="D20" s="14">
+        <v>360</v>
+      </c>
+      <c r="E20" s="14">
+        <v>50</v>
+      </c>
+      <c r="F20" s="14">
+        <v>250</v>
+      </c>
+      <c r="G20" s="14">
+        <v>5</v>
+      </c>
+      <c r="H20" s="14">
+        <v>50</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>40</v>
+      </c>
+      <c r="D21" s="14">
+        <v>300</v>
+      </c>
+      <c r="E21" s="14">
+        <v>65</v>
+      </c>
+      <c r="F21" s="14">
+        <v>400</v>
+      </c>
+      <c r="G21" s="14">
+        <v>8</v>
+      </c>
+      <c r="H21" s="14">
+        <v>50</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1275</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>165</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>

--- a/12600475.xlsx
+++ b/12600475.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git776\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0A940A-D7F7-48FF-808A-97AC4F667EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE5620C-CC95-4E52-B0FF-B098D965BCCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -242,6 +242,12 @@
   </si>
   <si>
     <t>good day</t>
+  </si>
+  <si>
+    <t>bad day</t>
+  </si>
+  <si>
+    <t>very bad day</t>
   </si>
 </sst>
 </file>
@@ -1757,70 +1763,142 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B22" s="14">
+        <v>240</v>
+      </c>
+      <c r="C22" s="14">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
+        <v>180</v>
+      </c>
+      <c r="E22" s="14">
+        <v>40</v>
+      </c>
+      <c r="F22" s="14">
+        <v>350</v>
+      </c>
+      <c r="G22" s="14">
+        <v>7</v>
+      </c>
+      <c r="H22" s="14">
+        <v>50</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B23" s="14">
+        <v>320</v>
+      </c>
+      <c r="C23" s="14">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>200</v>
+      </c>
+      <c r="E23" s="14">
+        <v>65</v>
+      </c>
+      <c r="F23" s="14">
+        <v>150</v>
+      </c>
+      <c r="G23" s="14">
+        <v>3</v>
+      </c>
+      <c r="H23" s="14">
+        <v>60</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>815</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>625</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B24" s="14">
+        <v>360</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>120</v>
+      </c>
+      <c r="E24" s="14">
+        <v>60</v>
+      </c>
+      <c r="F24" s="14">
+        <v>200</v>
+      </c>
+      <c r="G24" s="14">
+        <v>4</v>
+      </c>
+      <c r="H24" s="14">
+        <v>45</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>785</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>655</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
